--- a/data/gravel/Enve Mog 2025.xlsx
+++ b/data/gravel/Enve Mog 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36C66AE-2CAE-094F-A345-5BEC994C3AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FB8134-DAB1-8D42-AA61-385308B6D8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t>usd</t>
+  </si>
+  <si>
+    <t>https://enve.com/cdn/shop/files/ENVE-MY24-MOG_Sand_01_f9d13f94-2051-41e2-8e34-50d40f713146.jpg?v=1736889246&amp;width=1080</t>
   </si>
 </sst>
 </file>
@@ -735,6 +738,11 @@
         <v>105</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>110</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>

--- a/data/gravel/Enve Mog 2025.xlsx
+++ b/data/gravel/Enve Mog 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FB8134-DAB1-8D42-AA61-385308B6D8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB315E0-CCD0-4345-98F7-590D8E9BA4D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9880" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -349,10 +349,16 @@
     <t>yes</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>https://enve.com/cdn/shop/files/ENVE-MY24-MOG_Sand_01_f9d13f94-2051-41e2-8e34-50d40f713146.jpg?v=1736889246&amp;width=1080</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Ogden, Utah, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -692,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -740,7 +746,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1674,7 +1680,15 @@
         <v>98</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>110</v>
+      </c>
+      <c r="B76" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Enve Mog 2025.xlsx
+++ b/data/gravel/Enve Mog 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB315E0-CCD0-4345-98F7-590D8E9BA4D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A27394-95C9-7341-9436-9142934FC0E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9880" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -359,6 +359,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -698,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1514,136 +1532,121 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>75</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>77</v>
-      </c>
-      <c r="B54">
-        <v>27.2</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>78</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>79</v>
-      </c>
-      <c r="B56">
-        <v>50</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>81</v>
-      </c>
-      <c r="B58">
-        <v>180</v>
+        <v>75</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>82</v>
-      </c>
-      <c r="B59">
-        <v>160</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>83</v>
+        <v>77</v>
+      </c>
+      <c r="B60">
+        <v>27.2</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>85</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>107</v>
+        <v>79</v>
+      </c>
+      <c r="B62">
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>87</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>108</v>
+        <v>81</v>
+      </c>
+      <c r="B64">
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>89</v>
-      </c>
-      <c r="B66">
-        <v>1</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>91</v>
+        <v>85</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>92</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>108</v>
@@ -1651,43 +1654,88 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>94</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>108</v>
+        <v>88</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B72">
-        <v>4100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>96</v>
+        <v>90</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
+        <v>93</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>94</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>95</v>
+      </c>
+      <c r="B78">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>98</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>110</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B82" t="s">
         <v>111</v>
       </c>
     </row>
